--- a/input/timetable/Пед.образование-.xlsx
+++ b/input/timetable/Пед.образование-.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>

--- a/input/timetable/Пед.образование-.xlsx
+++ b/input/timetable/Пед.образование-.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="141">
   <si>
     <t>пара</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -134,6 +137,15 @@
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
+    <t>Муллер О.Ю.</t>
+  </si>
+  <si>
+    <t>Литовченко А.С.</t>
+  </si>
+  <si>
+    <t>Гаврилова Н.В.</t>
+  </si>
+  <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
@@ -143,6 +155,21 @@
     <t>Методика обучения и воспитания в технологическом образовании (пр), К437</t>
   </si>
   <si>
+    <t>Насырова Э.Ф.</t>
+  </si>
+  <si>
+    <t>Усольцева И.В.</t>
+  </si>
+  <si>
+    <t>Дроздова А.А.</t>
+  </si>
+  <si>
+    <t>Мойсеенкова М.А.</t>
+  </si>
+  <si>
+    <t>Варлакова Ю.Р.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
@@ -167,6 +194,15 @@
     <t>209-31</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
+    <t>Ткаченко Т.С.</t>
+  </si>
+  <si>
+    <t>Богач М.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 2, К427</t>
   </si>
   <si>
@@ -182,6 +218,9 @@
     <t>Психология (лек), К438</t>
   </si>
   <si>
+    <t>Демчук А.В.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (лек 16 ч)</t>
   </si>
   <si>
@@ -299,21 +338,42 @@
     <t>02.02.2026 - 08.04.2026</t>
   </si>
   <si>
+    <t>Ситникова А.Ю.</t>
+  </si>
+  <si>
     <t>Педагогическая риторика (лек), К438</t>
   </si>
   <si>
     <t>Педагогическая риторика (пр), К438</t>
   </si>
   <si>
+    <t>Мальков О.А.</t>
+  </si>
+  <si>
     <t>Психология (пр), К438//</t>
   </si>
   <si>
     <t>Основы изобразительного искусства (лек), К434</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Джумаева А.А.; Бастинович Е.В.</t>
+  </si>
+  <si>
     <t>Системы автоматизированного проектирования в технологическом образовании (лек)/(пр), К433</t>
   </si>
   <si>
+    <t>Ткаченко Т.С.; Мойсеенкова М.А</t>
+  </si>
+  <si>
+    <t>Ташманова Н.В.</t>
+  </si>
+  <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
     <t>ФТД: Цифровая грамотность (пр), К433</t>
   </si>
   <si>
@@ -323,12 +383,18 @@
     <t>Иностранный язык, п/г 2, К412</t>
   </si>
   <si>
+    <t>Гаврилова Н.В./Литовченко А.С.</t>
+  </si>
+  <si>
     <t>Технологии цифрового образования (лек), К433// Учебная практика, технологическая (проектно-технологическая) (8 ч), К433</t>
   </si>
   <si>
     <t>Технологии цифрового образования (пр)/(лек), К433</t>
   </si>
   <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
     <t>Экономика образования (пр), К438</t>
   </si>
   <si>
@@ -338,10 +404,16 @@
     <t>Иностранный язык, п/г 1, К426</t>
   </si>
   <si>
+    <t>Калинина Е.А./Плесовских И.Н.</t>
+  </si>
+  <si>
     <t>Философия (пр), К426// Работа в команде (пр), К426</t>
   </si>
   <si>
     <t>Иностранный язык в проф. сфере (24 ч), п/г 1, К425</t>
+  </si>
+  <si>
+    <t>Мойсеенкова М.А.;Ткаченко Т.С.</t>
   </si>
   <si>
     <t>Педагогика специального и инклюзивного образования (лек), К437</t>
@@ -486,7 +558,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,12 +577,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -627,6 +705,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -992,6 +1083,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1182,7 +1284,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1222,42 +1324,48 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1276,48 +1384,51 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1327,27 +1438,125 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1355,35 +1564,26 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1392,103 +1592,83 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1497,10 +1677,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1509,137 +1686,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1648,7 +1773,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1980,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1989,10 +2114,11 @@
     <col min="4" max="4" width="19.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2000,15 +2126,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2016,7 +2142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -2025,30 +2151,30 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2058,46 +2184,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="50" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="75" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-    </row>
-    <row r="9" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+      <c r="C8" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+    </row>
+    <row r="9" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+      <c r="C9" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
@@ -2108,339 +2234,409 @@
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="G10" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="25">
         <v>1</v>
       </c>
-      <c r="C11" s="76" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
-    </row>
-    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="138" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="80" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>2</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="81"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C12" s="93" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="85" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>3</v>
       </c>
-      <c r="C13" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="71"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
+      <c r="C13" s="131" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="82" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
         <v>4</v>
       </c>
-      <c r="C14" s="82" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="84"/>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="30">
+      <c r="C14" s="141" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="83" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="34">
         <v>1</v>
       </c>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="74"/>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C15" s="134"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="87"/>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>2</v>
       </c>
-      <c r="C16" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-    </row>
-    <row r="17" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="131" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28">
         <v>3</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-    </row>
-    <row r="18" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="28">
+      <c r="C17" s="131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="82" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="31">
         <v>4</v>
       </c>
-      <c r="C18" s="94"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="96"/>
-      <c r="L18" s="57"/>
-    </row>
-    <row r="19" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="30">
+      <c r="C18" s="111"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="81"/>
+      <c r="M18" s="64"/>
+    </row>
+    <row r="19" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="34">
         <v>1</v>
       </c>
-      <c r="C19" s="106" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="108"/>
-    </row>
-    <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="C19" s="123" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="80" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
         <v>3</v>
       </c>
-      <c r="C20" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="112"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C20" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="129"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28">
         <v>4</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="112"/>
-      <c r="E21" s="113" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="81"/>
-    </row>
-    <row r="22" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="31"/>
-      <c r="B22" s="28">
+      <c r="C21" s="93"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="130" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="95"/>
+      <c r="G21" s="79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="35"/>
+      <c r="B22" s="31">
         <v>5</v>
       </c>
-      <c r="C22" s="100"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="102"/>
-    </row>
-    <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="30">
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="74"/>
+    </row>
+    <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="34">
         <v>5</v>
       </c>
-      <c r="C23" s="109" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="111"/>
-    </row>
-    <row r="24" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="24">
+      <c r="C23" s="126" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="80" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="25">
         <v>6</v>
       </c>
-      <c r="C24" s="91" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92" t="s">
+      <c r="C24" s="108" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" s="110"/>
+      <c r="G24" s="79" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="122"/>
+      <c r="G25" s="73"/>
+    </row>
+    <row r="26" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="35"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="74"/>
+    </row>
+    <row r="27" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="34">
+        <v>2</v>
+      </c>
+      <c r="C27" s="123" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="85" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="28">
+        <v>3</v>
+      </c>
+      <c r="C28" s="131" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="82" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="28">
+        <v>4</v>
+      </c>
+      <c r="C29" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="37"/>
+      <c r="B30" s="31">
+        <v>5</v>
+      </c>
+      <c r="C30" s="99" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="81" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A31" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="34">
+        <v>1</v>
+      </c>
+      <c r="C31" s="114"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="26"/>
+    </row>
+    <row r="32" spans="1:13" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="39"/>
+      <c r="B32" s="28">
+        <v>2</v>
+      </c>
+      <c r="C32" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="95"/>
+      <c r="G32" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="93"/>
-    </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="105"/>
-    </row>
-    <row r="26" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="31"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="87"/>
-    </row>
-    <row r="27" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="30">
-        <v>2</v>
-      </c>
-      <c r="C27" s="106" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="108"/>
-    </row>
-    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32"/>
-      <c r="B28" s="26">
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="40"/>
+      <c r="B33" s="31">
         <v>3</v>
       </c>
-      <c r="C28" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71"/>
-    </row>
-    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32"/>
-      <c r="B29" s="26">
-        <v>4</v>
-      </c>
-      <c r="C29" s="79" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="81"/>
-    </row>
-    <row r="30" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="33"/>
-      <c r="B30" s="28">
-        <v>5</v>
-      </c>
-      <c r="C30" s="120" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="122"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A31" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="30">
-        <v>1</v>
-      </c>
-      <c r="C31" s="97"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="99"/>
-    </row>
-    <row r="32" spans="1:12" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="35"/>
-      <c r="B32" s="26">
-        <v>2</v>
-      </c>
-      <c r="C32" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="81"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="36"/>
-      <c r="B33" s="28">
-        <v>3</v>
-      </c>
-      <c r="C33" s="114"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
-      <c r="F33" s="116"/>
-    </row>
-    <row r="34" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="41"/>
-      <c r="B35" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="117" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="119"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="42"/>
-      <c r="B36" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="88" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="90"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="56"/>
-      <c r="B37" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="88" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="89"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="90"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="43"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="114"/>
-      <c r="D38" s="115"/>
-      <c r="E38" s="115"/>
-      <c r="F38" s="116"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="74"/>
+    </row>
+    <row r="34" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="41"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="45"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="46"/>
+      <c r="B35" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="97"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="88" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="47"/>
+      <c r="B36" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="102" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="82" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="63"/>
+      <c r="B37" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="84" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="48"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="32"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>14</v>
       </c>
@@ -2448,23 +2644,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C24:D24"/>
@@ -2481,14 +2678,13 @@
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2519,7 +2715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2528,10 +2724,11 @@
     <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2539,15 +2736,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2555,7 +2752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -2564,30 +2761,30 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2597,35 +2794,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="50" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="139" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+      <c r="C8" s="147" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -2636,330 +2833,388 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="68" t="s">
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="138" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="62"/>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28">
+        <v>4</v>
+      </c>
+      <c r="C11" s="131" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31">
+        <v>5</v>
+      </c>
+      <c r="C12" s="157"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="77"/>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="34">
+        <v>1</v>
+      </c>
+      <c r="C13" s="160"/>
+      <c r="D13" s="161"/>
+      <c r="E13" s="161"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="79"/>
+    </row>
+    <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
+        <v>2</v>
+      </c>
+      <c r="C14" s="144" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="79" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
+        <v>3</v>
+      </c>
+      <c r="C15" s="131" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="35"/>
+      <c r="B16" s="31">
+        <v>4</v>
+      </c>
+      <c r="C16" s="148"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="73"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="34">
+        <v>1</v>
+      </c>
+      <c r="C17" s="154"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="155"/>
+      <c r="F17" s="156"/>
+      <c r="G17" s="62"/>
+    </row>
+    <row r="18" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28">
+        <v>2</v>
+      </c>
+      <c r="C18" s="131" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="79" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
+        <v>3</v>
+      </c>
+      <c r="C19" s="131" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="79" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="35"/>
+      <c r="B20" s="31">
+        <v>4</v>
+      </c>
+      <c r="C20" s="151"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="74"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="134" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="79"/>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28">
+        <v>4</v>
+      </c>
+      <c r="C22" s="144" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="145"/>
+      <c r="E22" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="76" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="78"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="F22" s="146"/>
+      <c r="G22" s="85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="68"/>
+      <c r="B23" s="69">
+        <v>5</v>
+      </c>
+      <c r="C23" s="164"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="86"/>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="35"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="167"/>
+      <c r="D24" s="168"/>
+      <c r="E24" s="168"/>
+      <c r="F24" s="169"/>
+      <c r="G24" s="74"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="34">
+        <v>3</v>
+      </c>
+      <c r="C25" s="134" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="87" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="36"/>
+      <c r="B26" s="28">
         <v>4</v>
       </c>
-      <c r="C11" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="71"/>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C26" s="93" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="94"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="86" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="28">
         <v>5</v>
       </c>
-      <c r="C12" s="149"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="151"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="30">
+      <c r="C27" s="93" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="37"/>
+      <c r="B28" s="31">
+        <v>6</v>
+      </c>
+      <c r="C28" s="170"/>
+      <c r="D28" s="171"/>
+      <c r="E28" s="171"/>
+      <c r="F28" s="172"/>
+      <c r="G28" s="79"/>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="34">
         <v>1</v>
       </c>
-      <c r="C13" s="152"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="154"/>
-    </row>
-    <row r="14" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C29" s="134"/>
+      <c r="D29" s="135"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="62"/>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="39"/>
+      <c r="B30" s="28">
         <v>2</v>
       </c>
-      <c r="C14" s="136" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="138"/>
-    </row>
-    <row r="15" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="C30" s="144" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="40"/>
+      <c r="B31" s="31">
         <v>3</v>
       </c>
-      <c r="C15" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="71"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="31"/>
-      <c r="B16" s="28">
-        <v>4</v>
-      </c>
-      <c r="C16" s="140"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="142"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="30">
-        <v>1</v>
-      </c>
-      <c r="C17" s="146"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-    </row>
-    <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
-        <v>2</v>
-      </c>
-      <c r="C18" s="69" t="s">
+      <c r="C31" s="173" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="174"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
-    </row>
-    <row r="19" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
-        <v>3</v>
-      </c>
-      <c r="C19" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="71"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="31"/>
-      <c r="B20" s="28">
-        <v>4</v>
-      </c>
-      <c r="C20" s="143"/>
-      <c r="D20" s="144"/>
-      <c r="E20" s="144"/>
-      <c r="F20" s="145"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
-        <v>4</v>
-      </c>
-      <c r="C22" s="136" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="138"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="61"/>
-      <c r="B23" s="62">
-        <v>5</v>
-      </c>
-      <c r="C23" s="124"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="126"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="31"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="129"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="30">
-        <v>3</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="32"/>
-      <c r="B26" s="26">
-        <v>4</v>
-      </c>
-      <c r="C26" s="79" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="81"/>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="32"/>
-      <c r="B27" s="26">
-        <v>5</v>
-      </c>
-      <c r="C27" s="79" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="81"/>
-    </row>
-    <row r="28" spans="1:6" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="33"/>
-      <c r="B28" s="28">
-        <v>6</v>
-      </c>
-      <c r="C28" s="130"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="132"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="30">
-        <v>1</v>
-      </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="35"/>
-      <c r="B30" s="26">
-        <v>2</v>
-      </c>
-      <c r="C30" s="136" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="51"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="46"/>
+      <c r="B33" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="87" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="47"/>
+      <c r="B34" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="137"/>
-      <c r="E30" s="137"/>
-      <c r="F30" s="138"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="36"/>
-      <c r="B31" s="28">
-        <v>3</v>
-      </c>
-      <c r="C31" s="133" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" s="134"/>
-      <c r="E31" s="134"/>
-      <c r="F31" s="135"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="46"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="50"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="41"/>
-      <c r="B33" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="117" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="119"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="42"/>
-      <c r="B34" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="88" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="42"/>
-      <c r="B35" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="88" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="90"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="60"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="114"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="116"/>
-    </row>
-    <row r="37" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="59"/>
-      <c r="C37" s="123" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="123"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="47"/>
+      <c r="B35" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="85" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="67"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="77"/>
+    </row>
+    <row r="37" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="66"/>
+      <c r="C37" s="163" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="163"/>
+      <c r="E37" s="163"/>
+      <c r="F37" s="163"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
@@ -2967,16 +3222,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="C8:F8"/>
@@ -2992,20 +3261,6 @@
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3036,7 +3291,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3044,10 +3299,11 @@
     <col min="3" max="3" width="16.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
     <col min="5" max="6" width="16.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3055,15 +3311,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3071,7 +3327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -3080,30 +3336,30 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10">
@@ -3113,333 +3369,389 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="50" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="139" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+      <c r="C8" s="147" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="53"/>
-    </row>
-    <row r="10" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="30">
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="34">
         <v>1</v>
       </c>
-      <c r="C10" s="155" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="157"/>
-    </row>
-    <row r="11" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="190" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28">
         <v>2</v>
       </c>
-      <c r="C11" s="136" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="138"/>
-    </row>
-    <row r="12" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="144" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>3</v>
       </c>
-      <c r="C12" s="136" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="138"/>
-    </row>
-    <row r="13" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="31"/>
-      <c r="B13" s="28">
+      <c r="C12" s="144" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="35"/>
+      <c r="B13" s="31">
         <v>4</v>
       </c>
-      <c r="C13" s="164" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="165"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="167"/>
-    </row>
-    <row r="14" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="30">
+      <c r="C13" s="177" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="179"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="85" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="34">
         <v>3</v>
       </c>
-      <c r="C14" s="161"/>
-      <c r="D14" s="162"/>
-      <c r="E14" s="156" t="s">
-        <v>110</v>
-      </c>
-      <c r="F14" s="157"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="C14" s="196"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="191" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="192"/>
+      <c r="G14" s="87" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
         <v>4</v>
       </c>
-      <c r="C15" s="136" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="138"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C15" s="144" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>5</v>
       </c>
-      <c r="C16" s="136" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="138"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="31"/>
-      <c r="B17" s="28">
+      <c r="C16" s="144" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="35"/>
+      <c r="B17" s="31">
         <v>6</v>
       </c>
-      <c r="C17" s="158"/>
-      <c r="D17" s="159"/>
-      <c r="E17" s="159"/>
-      <c r="F17" s="160"/>
-    </row>
-    <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="30">
+      <c r="C17" s="193"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="81"/>
+    </row>
+    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="34">
         <v>1</v>
       </c>
-      <c r="C18" s="106" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
+      <c r="C18" s="123" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>2</v>
       </c>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="144" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="146"/>
+      <c r="G19" s="79" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
+        <v>3</v>
+      </c>
+      <c r="C20" s="144" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="79" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="35"/>
+      <c r="B21" s="31">
+        <v>4</v>
+      </c>
+      <c r="C21" s="105"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="74"/>
+    </row>
+    <row r="22" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="34">
+        <v>1</v>
+      </c>
+      <c r="C22" s="123" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="124"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="80" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
+        <v>2</v>
+      </c>
+      <c r="C23" s="144" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="79" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
+        <v>3</v>
+      </c>
+      <c r="C24" s="144" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="79" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="31">
+        <v>4</v>
+      </c>
+      <c r="C25" s="105"/>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="74"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="187" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="188"/>
+      <c r="E26" s="188"/>
+      <c r="F26" s="189"/>
+      <c r="G26" s="26"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="28">
+        <v>4</v>
+      </c>
+      <c r="C27" s="144" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="145"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="146"/>
+      <c r="G27" s="79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="28">
+        <v>5</v>
+      </c>
+      <c r="C28" s="144" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="37"/>
+      <c r="B29" s="31">
+        <v>6</v>
+      </c>
+      <c r="C29" s="184"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="185"/>
+      <c r="F29" s="186"/>
+      <c r="G29" s="32"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="34">
+        <v>1</v>
+      </c>
+      <c r="C30" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="97"/>
+      <c r="E30" s="97"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="26"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="39"/>
+      <c r="B31" s="28">
+        <v>2</v>
+      </c>
+      <c r="C31" s="181"/>
+      <c r="D31" s="182"/>
+      <c r="E31" s="182"/>
+      <c r="F31" s="183"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="40"/>
+      <c r="B32" s="31">
+        <v>3</v>
+      </c>
+      <c r="C32" s="90"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="32"/>
+    </row>
+    <row r="33" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="137"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="138"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>3</v>
-      </c>
-      <c r="C20" s="136" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="137"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="138"/>
-    </row>
-    <row r="21" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="31"/>
-      <c r="B21" s="28">
-        <v>4</v>
-      </c>
-      <c r="C21" s="85"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="87"/>
-    </row>
-    <row r="22" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="30">
-        <v>1</v>
-      </c>
-      <c r="C22" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="108"/>
-    </row>
-    <row r="23" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
-        <v>2</v>
-      </c>
-      <c r="C23" s="136" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="138"/>
-    </row>
-    <row r="24" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>3</v>
-      </c>
-      <c r="C24" s="136" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="138"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="31"/>
-      <c r="B25" s="28">
-        <v>4</v>
-      </c>
-      <c r="C25" s="85"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="87"/>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="174" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="175"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="176"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="32"/>
-      <c r="B27" s="26">
-        <v>4</v>
-      </c>
-      <c r="C27" s="136" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="138"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32"/>
-      <c r="B28" s="26">
-        <v>5</v>
-      </c>
-      <c r="C28" s="136" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" s="137"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="138"/>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="33"/>
-      <c r="B29" s="28">
-        <v>6</v>
-      </c>
-      <c r="C29" s="171"/>
-      <c r="D29" s="172"/>
-      <c r="E29" s="172"/>
-      <c r="F29" s="173"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="30">
-        <v>1</v>
-      </c>
-      <c r="C30" s="117" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="35"/>
-      <c r="B31" s="26">
-        <v>2</v>
-      </c>
-      <c r="C31" s="168"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="169"/>
-      <c r="F31" s="170"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="36"/>
-      <c r="B32" s="28">
-        <v>3</v>
-      </c>
-      <c r="C32" s="114"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="116"/>
-    </row>
-    <row r="33" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="163" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
-      <c r="F33" s="163"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="176" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="176"/>
+      <c r="E33" s="176"/>
+      <c r="F33" s="176"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B34" s="2" t="s">
@@ -3454,11 +3766,22 @@
         <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:F13"/>
@@ -3475,17 +3798,6 @@
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C18:F18"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:E5">
@@ -3516,7 +3828,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3525,10 +3837,11 @@
     <col min="4" max="4" width="18.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3536,15 +3849,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3552,7 +3865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -3561,30 +3874,30 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3594,374 +3907,443 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="50" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="54"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="61"/>
+      <c r="E8" s="60"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="139" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="139"/>
-      <c r="E9" s="54"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+      <c r="C9" s="147" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="147"/>
+      <c r="E9" s="60"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="53"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="D10" s="72"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="180" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="182"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="202" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="204"/>
+      <c r="G11" s="80" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>3</v>
       </c>
-      <c r="C12" s="136" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="138"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C12" s="144" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="79" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>4</v>
       </c>
-      <c r="C13" s="136" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="138"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="144" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="146"/>
+      <c r="G13" s="79" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
         <v>5</v>
       </c>
-      <c r="C14" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="92"/>
-      <c r="E14" s="92"/>
-      <c r="F14" s="93"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+      <c r="C14" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="79" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="30"/>
+      <c r="B15" s="31">
         <v>6</v>
       </c>
-      <c r="C15" s="183"/>
-      <c r="D15" s="166"/>
-      <c r="E15" s="166"/>
-      <c r="F15" s="167"/>
-    </row>
-    <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="30">
+      <c r="C15" s="205"/>
+      <c r="D15" s="179"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="180"/>
+      <c r="G15" s="79"/>
+    </row>
+    <row r="16" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="34">
         <v>1</v>
       </c>
-      <c r="C16" s="155" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="156"/>
-      <c r="E16" s="162"/>
-      <c r="F16" s="187"/>
-    </row>
-    <row r="17" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="190" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="191"/>
+      <c r="E16" s="197"/>
+      <c r="F16" s="198"/>
+      <c r="G16" s="80" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28">
         <v>2</v>
       </c>
-      <c r="C17" s="136" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="138"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="C17" s="144" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="145"/>
+      <c r="E17" s="145" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="146"/>
+      <c r="G17" s="85" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28">
         <v>3</v>
       </c>
-      <c r="C18" s="91" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="93"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
+      <c r="C18" s="108" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="109"/>
+      <c r="E18" s="109"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="79" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>4</v>
       </c>
-      <c r="C19" s="91" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="93"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="31"/>
-      <c r="B20" s="28">
+      <c r="C19" s="108" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="109"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="79" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="35"/>
+      <c r="B20" s="31">
         <v>5</v>
       </c>
-      <c r="C20" s="85"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="87"/>
-    </row>
-    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="C20" s="105"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="78"/>
+    </row>
+    <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="34">
         <v>2</v>
       </c>
-      <c r="C21" s="106" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="108"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
+      <c r="C21" s="123" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="88" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28">
         <v>3</v>
       </c>
-      <c r="C22" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="81"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
+      <c r="C22" s="93" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
         <v>4</v>
       </c>
-      <c r="C23" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="81"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
+      <c r="C23" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="79" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
         <v>5</v>
       </c>
-      <c r="C24" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="93"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="31"/>
-      <c r="B25" s="28">
+      <c r="C24" s="108" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="79" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="31">
         <v>6</v>
       </c>
-      <c r="C25" s="177"/>
-      <c r="D25" s="178"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="179"/>
-    </row>
-    <row r="26" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="30">
+      <c r="C25" s="199"/>
+      <c r="D25" s="200"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="201"/>
+      <c r="G25" s="32"/>
+    </row>
+    <row r="26" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="34">
         <v>2</v>
       </c>
-      <c r="C26" s="109" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="111"/>
-    </row>
-    <row r="27" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26">
+      <c r="C26" s="126" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="127"/>
+      <c r="E26" s="127"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="80" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28">
         <v>3</v>
       </c>
-      <c r="C27" s="136" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="138"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="25"/>
-      <c r="B28" s="26">
+      <c r="C27" s="144" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="145"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="146"/>
+      <c r="G27" s="79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="27"/>
+      <c r="B28" s="28">
         <v>4</v>
       </c>
-      <c r="C28" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="93"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="31"/>
-      <c r="B29" s="28">
+      <c r="C28" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="35"/>
+      <c r="B29" s="31">
         <v>5</v>
       </c>
-      <c r="C29" s="184" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="186"/>
-    </row>
-    <row r="30" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="30">
+      <c r="C29" s="206" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="207"/>
+      <c r="E29" s="207"/>
+      <c r="F29" s="208"/>
+      <c r="G29" s="79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="34">
         <v>2</v>
       </c>
-      <c r="C30" s="146"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="110" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="111"/>
-    </row>
-    <row r="31" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="32"/>
-      <c r="B31" s="26">
+      <c r="C30" s="154"/>
+      <c r="D30" s="155"/>
+      <c r="E30" s="127" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="128"/>
+      <c r="G30" s="80" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="36"/>
+      <c r="B31" s="28">
         <v>3</v>
       </c>
-      <c r="C31" s="136" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="137"/>
-      <c r="E31" s="137" t="s">
-        <v>108</v>
-      </c>
-      <c r="F31" s="138"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="32"/>
-      <c r="B32" s="26">
+      <c r="C31" s="144" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="145"/>
+      <c r="E31" s="145" t="s">
+        <v>132</v>
+      </c>
+      <c r="F31" s="146"/>
+      <c r="G31" s="85" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="36"/>
+      <c r="B32" s="28">
         <v>4</v>
       </c>
-      <c r="C32" s="136" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="138"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="33"/>
-      <c r="B33" s="28">
+      <c r="C32" s="144" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="146"/>
+      <c r="G32" s="79" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="37"/>
+      <c r="B33" s="31">
         <v>5</v>
       </c>
-      <c r="C33" s="94" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="95"/>
-      <c r="E33" s="95"/>
-      <c r="F33" s="96"/>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="30">
+      <c r="C33" s="111" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="79" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="34">
         <v>1</v>
       </c>
-      <c r="C34" s="117" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="119"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="35"/>
-      <c r="B35" s="26">
+      <c r="C34" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="97"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="26"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="39"/>
+      <c r="B35" s="28">
         <v>2</v>
       </c>
-      <c r="C35" s="103"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="105"/>
-    </row>
-    <row r="36" spans="1:6" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="36"/>
-      <c r="B36" s="28">
+      <c r="C35" s="120"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="82"/>
+    </row>
+    <row r="36" spans="1:7" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="40"/>
+      <c r="B36" s="31">
         <v>3</v>
       </c>
-      <c r="C36" s="143"/>
-      <c r="D36" s="144"/>
-      <c r="E36" s="144"/>
-      <c r="F36" s="145"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C36" s="151"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="83"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>14</v>
       </c>
@@ -3969,31 +4351,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C24:F24"/>
@@ -4010,6 +4377,21 @@
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
